--- a/КМ, л.р. 3, функция интенсивности.xlsx
+++ b/КМ, л.р. 3, функция интенсивности.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxim\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Загрузки\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63621B69-A42F-45D5-8F27-20AF2339F006}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EF85F15-E48D-430D-BF10-6493ECCC2C85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -45,13 +45,13 @@
     <t>[14, 18)</t>
   </si>
   <si>
-    <t>[18, 20)</t>
-  </si>
-  <si>
     <t>Функция интенсивности</t>
   </si>
   <si>
     <t>График функции интенсивности</t>
+  </si>
+  <si>
+    <t>[18, 20)</t>
   </si>
 </sst>
 </file>
@@ -91,7 +91,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="26">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -278,62 +278,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="medium">
@@ -383,34 +327,73 @@
     </border>
     <border>
       <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
       <top style="medium">
         <color indexed="64"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
-      <right style="thin">
+      <right style="medium">
         <color indexed="64"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
         <color indexed="64"/>
       </top>
       <bottom style="medium">
@@ -422,23 +405,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -451,25 +419,52 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -478,16 +473,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
@@ -496,29 +488,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -574,10 +551,10 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Лист1!$D$10:$X$10</c:f>
+              <c:f>Лист1!$D$10:$W$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="21"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -637,42 +614,39 @@
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>19</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>20</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Лист1!$D$11:$X$11</c:f>
+              <c:f>Лист1!$D$11:$W$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="21"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>10</c:v>
@@ -687,31 +661,28 @@
                   <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="12">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>20</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="15">
                   <c:v>20</c:v>
                 </c:pt>
-                <c:pt idx="14">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>10</c:v>
-                </c:pt>
                 <c:pt idx="16">
-                  <c:v>10</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>10</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>15</c:v>
+                  <c:v>30</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>15</c:v>
+                  <c:v>30</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1471,15 +1442,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:colOff>57150</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>34290</xdr:rowOff>
+      <xdr:rowOff>15239</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>365760</xdr:colOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>314325</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>205740</xdr:rowOff>
+      <xdr:rowOff>200024</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1770,371 +1741,357 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:X21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="B1:X20"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.77734375" customWidth="1"/>
-    <col min="2" max="3" width="15.77734375" customWidth="1"/>
-    <col min="4" max="27" width="5.77734375" customWidth="1"/>
-    <col min="28" max="50" width="10.77734375" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" customWidth="1"/>
+    <col min="2" max="3" width="15.7109375" customWidth="1"/>
+    <col min="4" max="24" width="5.7109375" customWidth="1"/>
+    <col min="25" max="46" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:24" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:24" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B2" s="27" t="s">
+    <row r="1" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:24" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="16"/>
+      <c r="E2" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="28"/>
-      <c r="E2" s="24" t="s">
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="28"/>
+      <c r="L2" s="28"/>
+      <c r="M2" s="28"/>
+      <c r="N2" s="28"/>
+      <c r="O2" s="28"/>
+      <c r="P2" s="28"/>
+      <c r="Q2" s="28"/>
+      <c r="R2" s="28"/>
+      <c r="S2" s="28"/>
+      <c r="T2" s="28"/>
+      <c r="U2" s="28"/>
+      <c r="V2" s="28"/>
+      <c r="W2" s="29"/>
+      <c r="X2" s="12"/>
+    </row>
+    <row r="3" spans="2:24" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="19"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
+      <c r="J3" s="20"/>
+      <c r="K3" s="20"/>
+      <c r="L3" s="20"/>
+      <c r="M3" s="20"/>
+      <c r="N3" s="20"/>
+      <c r="O3" s="20"/>
+      <c r="P3" s="20"/>
+      <c r="Q3" s="20"/>
+      <c r="R3" s="20"/>
+      <c r="S3" s="20"/>
+      <c r="T3" s="20"/>
+      <c r="U3" s="20"/>
+      <c r="V3" s="20"/>
+      <c r="W3" s="21"/>
+    </row>
+    <row r="4" spans="2:24" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6">
+        <v>0</v>
+      </c>
+      <c r="E4" s="22"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="30"/>
+      <c r="H4" s="30"/>
+      <c r="I4" s="30"/>
+      <c r="J4" s="30"/>
+      <c r="K4" s="30"/>
+      <c r="L4" s="30"/>
+      <c r="M4" s="30"/>
+      <c r="N4" s="30"/>
+      <c r="O4" s="30"/>
+      <c r="P4" s="30"/>
+      <c r="Q4" s="30"/>
+      <c r="R4" s="30"/>
+      <c r="S4" s="30"/>
+      <c r="T4" s="30"/>
+      <c r="U4" s="30"/>
+      <c r="V4" s="30"/>
+      <c r="W4" s="23"/>
+    </row>
+    <row r="5" spans="2:24" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="2">
+        <v>10</v>
+      </c>
+      <c r="E5" s="22"/>
+      <c r="F5" s="30"/>
+      <c r="G5" s="30"/>
+      <c r="H5" s="30"/>
+      <c r="I5" s="30"/>
+      <c r="J5" s="30"/>
+      <c r="K5" s="30"/>
+      <c r="L5" s="30"/>
+      <c r="M5" s="30"/>
+      <c r="N5" s="30"/>
+      <c r="O5" s="30"/>
+      <c r="P5" s="30"/>
+      <c r="Q5" s="30"/>
+      <c r="R5" s="30"/>
+      <c r="S5" s="30"/>
+      <c r="T5" s="30"/>
+      <c r="U5" s="30"/>
+      <c r="V5" s="30"/>
+      <c r="W5" s="23"/>
+    </row>
+    <row r="6" spans="2:24" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="2">
+        <v>40</v>
+      </c>
+      <c r="E6" s="22"/>
+      <c r="F6" s="30"/>
+      <c r="G6" s="30"/>
+      <c r="H6" s="30"/>
+      <c r="I6" s="30"/>
+      <c r="J6" s="30"/>
+      <c r="K6" s="30"/>
+      <c r="L6" s="30"/>
+      <c r="M6" s="30"/>
+      <c r="N6" s="30"/>
+      <c r="O6" s="30"/>
+      <c r="P6" s="30"/>
+      <c r="Q6" s="30"/>
+      <c r="R6" s="30"/>
+      <c r="S6" s="30"/>
+      <c r="T6" s="30"/>
+      <c r="U6" s="30"/>
+      <c r="V6" s="30"/>
+      <c r="W6" s="23"/>
+    </row>
+    <row r="7" spans="2:24" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="2">
+        <v>20</v>
+      </c>
+      <c r="E7" s="22"/>
+      <c r="F7" s="30"/>
+      <c r="G7" s="30"/>
+      <c r="H7" s="30"/>
+      <c r="I7" s="30"/>
+      <c r="J7" s="30"/>
+      <c r="K7" s="30"/>
+      <c r="L7" s="30"/>
+      <c r="M7" s="30"/>
+      <c r="N7" s="30"/>
+      <c r="O7" s="30"/>
+      <c r="P7" s="30"/>
+      <c r="Q7" s="30"/>
+      <c r="R7" s="30"/>
+      <c r="S7" s="30"/>
+      <c r="T7" s="30"/>
+      <c r="U7" s="30"/>
+      <c r="V7" s="30"/>
+      <c r="W7" s="23"/>
+    </row>
+    <row r="8" spans="2:24" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
-      <c r="M2" s="25"/>
-      <c r="N2" s="25"/>
-      <c r="O2" s="25"/>
-      <c r="P2" s="25"/>
-      <c r="Q2" s="25"/>
-      <c r="R2" s="25"/>
-      <c r="S2" s="25"/>
-      <c r="T2" s="25"/>
-      <c r="U2" s="25"/>
-      <c r="V2" s="25"/>
-      <c r="W2" s="25"/>
-      <c r="X2" s="26"/>
+      <c r="C8" s="4">
+        <v>30</v>
+      </c>
+      <c r="E8" s="24"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="25"/>
+      <c r="H8" s="25"/>
+      <c r="I8" s="25"/>
+      <c r="J8" s="25"/>
+      <c r="K8" s="25"/>
+      <c r="L8" s="25"/>
+      <c r="M8" s="25"/>
+      <c r="N8" s="25"/>
+      <c r="O8" s="25"/>
+      <c r="P8" s="25"/>
+      <c r="Q8" s="25"/>
+      <c r="R8" s="25"/>
+      <c r="S8" s="25"/>
+      <c r="T8" s="25"/>
+      <c r="U8" s="25"/>
+      <c r="V8" s="25"/>
+      <c r="W8" s="26"/>
     </row>
-    <row r="3" spans="2:24" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="2" t="s">
+    <row r="9" spans="2:24" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="10" spans="2:24" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C10" s="18"/>
+      <c r="D10" s="10">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5">
         <v>1</v>
       </c>
-      <c r="E3" s="15"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16"/>
-      <c r="I3" s="16"/>
-      <c r="J3" s="16"/>
-      <c r="K3" s="16"/>
-      <c r="L3" s="16"/>
-      <c r="M3" s="16"/>
-      <c r="N3" s="16"/>
-      <c r="O3" s="16"/>
-      <c r="P3" s="16"/>
-      <c r="Q3" s="16"/>
-      <c r="R3" s="16"/>
-      <c r="S3" s="16"/>
-      <c r="T3" s="16"/>
-      <c r="U3" s="16"/>
-      <c r="V3" s="16"/>
-      <c r="W3" s="16"/>
-      <c r="X3" s="17"/>
+      <c r="F10" s="5">
+        <v>2</v>
+      </c>
+      <c r="G10" s="5">
+        <v>3</v>
+      </c>
+      <c r="H10" s="5">
+        <v>4</v>
+      </c>
+      <c r="I10" s="5">
+        <v>5</v>
+      </c>
+      <c r="J10" s="5">
+        <v>6</v>
+      </c>
+      <c r="K10" s="5">
+        <v>7</v>
+      </c>
+      <c r="L10" s="5">
+        <v>8</v>
+      </c>
+      <c r="M10" s="5">
+        <v>9</v>
+      </c>
+      <c r="N10" s="5">
+        <v>10</v>
+      </c>
+      <c r="O10" s="5">
+        <v>11</v>
+      </c>
+      <c r="P10" s="5">
+        <v>12</v>
+      </c>
+      <c r="Q10" s="5">
+        <v>13</v>
+      </c>
+      <c r="R10" s="5">
+        <v>14</v>
+      </c>
+      <c r="S10" s="5">
+        <v>15</v>
+      </c>
+      <c r="T10" s="5">
+        <v>16</v>
+      </c>
+      <c r="U10" s="5">
+        <v>17</v>
+      </c>
+      <c r="V10" s="5">
+        <v>18</v>
+      </c>
+      <c r="W10" s="6">
+        <v>19</v>
+      </c>
+      <c r="X10" s="11"/>
     </row>
-    <row r="4" spans="2:24" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" s="5">
+    <row r="11" spans="2:24" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="18"/>
-      <c r="F4" s="19"/>
-      <c r="G4" s="19"/>
-      <c r="H4" s="19"/>
-      <c r="I4" s="19"/>
-      <c r="J4" s="19"/>
-      <c r="K4" s="19"/>
-      <c r="L4" s="19"/>
-      <c r="M4" s="19"/>
-      <c r="N4" s="19"/>
-      <c r="O4" s="19"/>
-      <c r="P4" s="19"/>
-      <c r="Q4" s="19"/>
-      <c r="R4" s="19"/>
-      <c r="S4" s="19"/>
-      <c r="T4" s="19"/>
-      <c r="U4" s="19"/>
-      <c r="V4" s="19"/>
-      <c r="W4" s="19"/>
-      <c r="X4" s="20"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="3">
+        <v>0</v>
+      </c>
+      <c r="E11" s="7">
+        <v>0</v>
+      </c>
+      <c r="F11" s="7">
+        <v>0</v>
+      </c>
+      <c r="G11" s="7">
+        <v>0</v>
+      </c>
+      <c r="H11" s="7">
+        <v>0</v>
+      </c>
+      <c r="I11" s="7">
+        <v>0</v>
+      </c>
+      <c r="J11" s="7">
+        <v>0</v>
+      </c>
+      <c r="K11" s="7">
+        <v>0</v>
+      </c>
+      <c r="L11" s="7">
+        <v>10</v>
+      </c>
+      <c r="M11" s="7">
+        <v>10</v>
+      </c>
+      <c r="N11" s="7">
+        <v>10</v>
+      </c>
+      <c r="O11" s="7">
+        <v>10</v>
+      </c>
+      <c r="P11" s="7">
+        <v>40</v>
+      </c>
+      <c r="Q11" s="7">
+        <v>40</v>
+      </c>
+      <c r="R11" s="7">
+        <v>20</v>
+      </c>
+      <c r="S11" s="7">
+        <v>20</v>
+      </c>
+      <c r="T11" s="7">
+        <v>20</v>
+      </c>
+      <c r="U11" s="7">
+        <v>20</v>
+      </c>
+      <c r="V11" s="7">
+        <v>30</v>
+      </c>
+      <c r="W11" s="4">
+        <v>30</v>
+      </c>
+      <c r="X11" s="11"/>
     </row>
-    <row r="5" spans="2:24" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" s="7">
-        <v>10</v>
-      </c>
-      <c r="E5" s="18"/>
-      <c r="F5" s="19"/>
-      <c r="G5" s="19"/>
-      <c r="H5" s="19"/>
-      <c r="I5" s="19"/>
-      <c r="J5" s="19"/>
-      <c r="K5" s="19"/>
-      <c r="L5" s="19"/>
-      <c r="M5" s="19"/>
-      <c r="N5" s="19"/>
-      <c r="O5" s="19"/>
-      <c r="P5" s="19"/>
-      <c r="Q5" s="19"/>
-      <c r="R5" s="19"/>
-      <c r="S5" s="19"/>
-      <c r="T5" s="19"/>
-      <c r="U5" s="19"/>
-      <c r="V5" s="19"/>
-      <c r="W5" s="19"/>
-      <c r="X5" s="20"/>
-    </row>
-    <row r="6" spans="2:24" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="7">
-        <v>20</v>
-      </c>
-      <c r="E6" s="18"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="19"/>
-      <c r="H6" s="19"/>
-      <c r="I6" s="19"/>
-      <c r="J6" s="19"/>
-      <c r="K6" s="19"/>
-      <c r="L6" s="19"/>
-      <c r="M6" s="19"/>
-      <c r="N6" s="19"/>
-      <c r="O6" s="19"/>
-      <c r="P6" s="19"/>
-      <c r="Q6" s="19"/>
-      <c r="R6" s="19"/>
-      <c r="S6" s="19"/>
-      <c r="T6" s="19"/>
-      <c r="U6" s="19"/>
-      <c r="V6" s="19"/>
-      <c r="W6" s="19"/>
-      <c r="X6" s="20"/>
-    </row>
-    <row r="7" spans="2:24" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="7">
-        <v>10</v>
-      </c>
-      <c r="E7" s="18"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="19"/>
-      <c r="H7" s="19"/>
-      <c r="I7" s="19"/>
-      <c r="J7" s="19"/>
-      <c r="K7" s="19"/>
-      <c r="L7" s="19"/>
-      <c r="M7" s="19"/>
-      <c r="N7" s="19"/>
-      <c r="O7" s="19"/>
-      <c r="P7" s="19"/>
-      <c r="Q7" s="19"/>
-      <c r="R7" s="19"/>
-      <c r="S7" s="19"/>
-      <c r="T7" s="19"/>
-      <c r="U7" s="19"/>
-      <c r="V7" s="19"/>
-      <c r="W7" s="19"/>
-      <c r="X7" s="20"/>
-    </row>
-    <row r="8" spans="2:24" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="9">
-        <v>15</v>
-      </c>
-      <c r="E8" s="21"/>
-      <c r="F8" s="22"/>
-      <c r="G8" s="22"/>
-      <c r="H8" s="22"/>
-      <c r="I8" s="22"/>
-      <c r="J8" s="22"/>
-      <c r="K8" s="22"/>
-      <c r="L8" s="22"/>
-      <c r="M8" s="22"/>
-      <c r="N8" s="22"/>
-      <c r="O8" s="22"/>
-      <c r="P8" s="22"/>
-      <c r="Q8" s="22"/>
-      <c r="R8" s="22"/>
-      <c r="S8" s="22"/>
-      <c r="T8" s="22"/>
-      <c r="U8" s="22"/>
-      <c r="V8" s="22"/>
-      <c r="W8" s="22"/>
-      <c r="X8" s="23"/>
-    </row>
-    <row r="9" spans="2:24" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-    </row>
-    <row r="10" spans="2:24" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="C10" s="30"/>
-      <c r="D10" s="13">
-        <v>0</v>
-      </c>
-      <c r="E10" s="10">
-        <v>1</v>
-      </c>
-      <c r="F10" s="10">
-        <v>2</v>
-      </c>
-      <c r="G10" s="10">
-        <v>3</v>
-      </c>
-      <c r="H10" s="10">
-        <v>4</v>
-      </c>
-      <c r="I10" s="10">
-        <v>5</v>
-      </c>
-      <c r="J10" s="10">
-        <v>6</v>
-      </c>
-      <c r="K10" s="10">
-        <v>7</v>
-      </c>
-      <c r="L10" s="10">
-        <v>8</v>
-      </c>
-      <c r="M10" s="10">
-        <v>9</v>
-      </c>
-      <c r="N10" s="10">
-        <v>10</v>
-      </c>
-      <c r="O10" s="10">
-        <v>11</v>
-      </c>
-      <c r="P10" s="10">
-        <v>12</v>
-      </c>
-      <c r="Q10" s="10">
-        <v>13</v>
-      </c>
-      <c r="R10" s="10">
-        <v>14</v>
-      </c>
-      <c r="S10" s="10">
-        <v>15</v>
-      </c>
-      <c r="T10" s="10">
-        <v>16</v>
-      </c>
-      <c r="U10" s="10">
-        <v>17</v>
-      </c>
-      <c r="V10" s="10">
-        <v>18</v>
-      </c>
-      <c r="W10" s="10">
-        <v>19</v>
-      </c>
-      <c r="X10" s="11">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="2:24" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C11" s="32"/>
-      <c r="D11" s="14">
-        <v>1</v>
-      </c>
-      <c r="E11" s="12">
-        <v>1</v>
-      </c>
-      <c r="F11" s="12">
-        <v>1</v>
-      </c>
-      <c r="G11" s="12">
-        <v>1</v>
-      </c>
-      <c r="H11" s="12">
-        <v>1</v>
-      </c>
-      <c r="I11" s="12">
-        <v>1</v>
-      </c>
-      <c r="J11" s="12">
-        <v>1</v>
-      </c>
-      <c r="K11" s="12">
-        <v>1</v>
-      </c>
-      <c r="L11" s="12">
-        <v>10</v>
-      </c>
-      <c r="M11" s="12">
-        <v>10</v>
-      </c>
-      <c r="N11" s="12">
-        <v>10</v>
-      </c>
-      <c r="O11" s="12">
-        <v>10</v>
-      </c>
-      <c r="P11" s="12">
-        <v>20</v>
-      </c>
-      <c r="Q11" s="12">
-        <v>20</v>
-      </c>
-      <c r="R11" s="12">
-        <v>10</v>
-      </c>
-      <c r="S11" s="12">
-        <v>10</v>
-      </c>
-      <c r="T11" s="12">
-        <v>10</v>
-      </c>
-      <c r="U11" s="12">
-        <v>10</v>
-      </c>
-      <c r="V11" s="12">
-        <v>15</v>
-      </c>
-      <c r="W11" s="12">
-        <v>15</v>
-      </c>
-      <c r="X11" s="9">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="2:24" ht="19.95" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="2:24" ht="19.95" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="2:24" ht="19.95" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="15" spans="2:24" ht="19.95" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="16" spans="2:24" ht="19.95" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="17" ht="19.95" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="18" ht="19.95" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="19" ht="19.95" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="20" ht="19.95" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="21" ht="19.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="12" spans="2:24" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="2:24" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="2:24" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="2:24" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="2:24" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="18" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="19" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="E3:X8"/>
-    <mergeCell ref="E2:X2"/>
+    <mergeCell ref="B11:C11"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="E3:W8"/>
+    <mergeCell ref="E2:W2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
